--- a/PROG - NORCOAST NC BRAVO 027S-01.xlsx
+++ b/PROG - NORCOAST NC BRAVO 027S-01.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hfern\OneDrive\Área de Trabalho\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hfern\OneDrive\Área de Trabalho\Viagens\NC BRAVO 027S\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD2CDC7C-8D3C-4583-85F6-71B426123263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADA5A96-0C9D-4590-86A9-E9F78E1D8397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F572F6F-2C46-4D4A-B012-D55B5063D1B2}"/>
   </bookViews>
@@ -96,9 +96,6 @@
     <t>NORCOAST LOGISTICA S.A</t>
   </si>
   <si>
-    <t>49.009.424/0008-82</t>
-  </si>
-  <si>
     <t>BRMAO</t>
   </si>
   <si>
@@ -202,6 +199,9 @@
   </si>
   <si>
     <t>COOPERCARGA</t>
+  </si>
+  <si>
+    <t>49.009.424/0001-06</t>
   </si>
 </sst>
 </file>
@@ -685,13 +685,13 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -700,13 +700,13 @@
         <v>53351724</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>11</v>
@@ -718,18 +718,18 @@
         <v>17</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -738,13 +738,13 @@
         <v>31021811</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
@@ -756,21 +756,21 @@
         <v>17</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -779,13 +779,13 @@
         <v>97080602</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>11</v>
@@ -797,21 +797,21 @@
         <v>17</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -820,13 +820,13 @@
         <v>97080602</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>11</v>
@@ -838,21 +838,21 @@
         <v>17</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -861,13 +861,13 @@
         <v>20402341</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>11</v>
@@ -879,21 +879,21 @@
         <v>17</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -902,13 +902,13 @@
         <v>93708889</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>11</v>
@@ -920,36 +920,36 @@
         <v>17</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1">
         <v>49069671</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>11</v>
@@ -961,33 +961,33 @@
         <v>17</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1">
         <v>96609258</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>11</v>
@@ -999,18 +999,18 @@
         <v>17</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -1019,13 +1019,13 @@
         <v>93708889</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>11</v>
@@ -1037,21 +1037,21 @@
         <v>17</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>15</v>
@@ -1060,13 +1060,13 @@
         <v>39626543</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>11</v>
@@ -1078,10 +1078,10 @@
         <v>17</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/PROG - NORCOAST NC BRAVO 027S-01.xlsx
+++ b/PROG - NORCOAST NC BRAVO 027S-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hfern\OneDrive\Área de Trabalho\Viagens\NC BRAVO 027S\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADA5A96-0C9D-4590-86A9-E9F78E1D8397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9153E408-92FC-4669-A82F-4A0153E41485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5F572F6F-2C46-4D4A-B012-D55B5063D1B2}"/>
+    <workbookView xWindow="5556" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{5F572F6F-2C46-4D4A-B012-D55B5063D1B2}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="52">
   <si>
     <t>POL</t>
   </si>
@@ -192,13 +192,7 @@
     <t xml:space="preserve">39626543G </t>
   </si>
   <si>
-    <t>00.468.285/0001-90</t>
-  </si>
-  <si>
     <t>49.009.424/0009-82</t>
-  </si>
-  <si>
-    <t>COOPERCARGA</t>
   </si>
   <si>
     <t>49.009.424/0001-06</t>
@@ -208,7 +202,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,6 +212,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -243,9 +245,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -717,9 +722,6 @@
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>50</v>
-      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -756,9 +758,6 @@
         <v>17</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -797,10 +796,7 @@
         <v>17</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -838,10 +834,7 @@
         <v>17</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -879,10 +872,7 @@
         <v>17</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -920,10 +910,7 @@
         <v>17</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -936,8 +923,8 @@
       <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
-        <v>52</v>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="E8" s="1">
         <v>49069671</v>
@@ -961,7 +948,7 @@
         <v>17</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -974,8 +961,8 @@
       <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="s">
-        <v>52</v>
+      <c r="D9" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E9" s="1">
         <v>96609258</v>
@@ -999,7 +986,7 @@
         <v>17</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1037,10 +1024,7 @@
         <v>17</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1078,10 +1062,7 @@
         <v>17</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
